--- a/reports/devops-jobs-israel-2026-W23.xlsx
+++ b/reports/devops-jobs-israel-2026-W23.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-01T11:52:53</t>
+    <t xml:space="preserve">2026-06-02T10:52:13</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,15 +57,12 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9%</t>
+    <t xml:space="preserve">0.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0%</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -258,6 +255,18 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
   </si>
   <si>
+    <t xml:space="preserve">Professional Services DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Professional Services DevOps Engineer</t>
   </si>
   <si>
@@ -399,6 +408,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer (Remote)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, Massachusetts, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Data Platform Engineer</t>
   </si>
   <si>
@@ -408,9 +432,6 @@
     <t xml:space="preserve">Lisbon</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
   </si>
   <si>
@@ -504,7 +525,7 @@
     <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
   </si>
   <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablemen</t>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
   </si>
   <si>
     <t xml:space="preserve">Melio</t>
@@ -525,6 +546,42 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kaltura</t>
   </si>
   <si>
@@ -534,124 +591,436 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
   </si>
   <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autodesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4420959611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4421807840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4418706383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grip Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-datateam-4421661564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, EWAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-ewaf-at-thales-4345712736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist - 50400194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Financial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloudops-engineer-at-moveo-source-4423883581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4417616930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-rafael-advanced-defense-systems-4421614338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linnovate Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4421620393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4409576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4416809451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4418395173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Be'er Sheva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberArk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-be-er-sheva-at-cyberark-4378443169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer (Cortex Research)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-cortex-research-at-palo-alto-networks-4361488662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Lead Engineer (DevOps and Process Optimization/Automation) – Bangkok based, relocation provided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-engineer-devops-and-process-optimization-automation-%E2%80%93-bangkok-based-relocation-provided-at-agoda-4411338565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure &amp; AKS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-aks-at-one-digital-4419243639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-engineer-at-gotfriends-4418384231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Cast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
+  </si>
+  <si>
     <t xml:space="preserve">Commit</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4421628183</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4Cast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4415246112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Yokneam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-yokneam-at-codevalue-4421696969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloudride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agentic DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empire Media Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/agentic-devops-at-empire-media-network-4418951731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4419826411</t>
+    <t xml:space="preserve">CodSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramla, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4422328952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4417624412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Cloud Architect (25000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25000-at-yael-group-4417626508</t>
   </si>
   <si>
     <t xml:space="preserve">IT DevOps Engineer</t>
@@ -666,660 +1035,366 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-mobileye-4409774817</t>
   </si>
   <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4418734554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-datateam-4421661564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grip Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 50% Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-core-team-at-thales-4371458115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4409726747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPC Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-cloud-engineer-at-opc-energy-4422582076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Shemesh, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4418249612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4419247188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377765290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-50%25-position-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist - 50400194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Financial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, EWAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-ewaf-at-thales-4345712736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4421648840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (New Ventures)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-new-ventures-at-monday-com-4419814790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead SRE, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-corsa-4419470455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4418564684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiBob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stampli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stampli-4421625305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer - Cloud, XSPM (Hybrid, ISR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-cloud-xspm-hybrid-isr-at-crowdstrike-4418750800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
   </si>
   <si>
     <t xml:space="preserve">Radware</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer (Cortex Research)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-cortex-research-at-palo-alto-networks-4361488662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Lead Engineer (DevOps and Process Optimization/Automation) – Bangkok based, relocation provided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agoda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-engineer-devops-and-process-optimization-automation-%E2%80%93-bangkok-based-relocation-provided-at-agoda-4411338565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensi.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4419063857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – Cloud &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michal Recruiting &amp; Placement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-cloud-infrastructure-at-michal-recruiting-placement-4421333933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4419075232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Cloud Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-platform-at-monday-com-4419824552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4420959611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4421807840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4418706383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4409766498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linnovate Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4421620393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-native-4418239509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CRM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-crm-at-monday-com-4419805943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finubit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-finubit-4420486202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XTEND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4421663350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-apple-4421047611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Shemesh, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4418249612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer (620127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpearUAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-620127-at-spearuav-4417648068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-corsa-4419470455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4417624412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4418564684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stampli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stampli-4421625305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiBob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-gong-4418991840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-rafael-advanced-defense-systems-4421614338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1335,79 +1410,73 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Fortinet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst- Student position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Cloud (any), CI/CD, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8572315002?gh_jid=8572315002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Specialist - Temporary position</t>
@@ -1428,6 +1497,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Specialist - Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orca AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-tier-2-at-orca-ai-4409854863</t>
+  </si>
+  <si>
     <t xml:space="preserve">Global Service Desk Representative</t>
   </si>
   <si>
@@ -1437,76 +1518,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
   </si>
   <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1515,25 +1536,28 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1685,7 +1709,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -1693,7 +1717,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1701,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -1709,7 +1733,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10">
@@ -1717,7 +1741,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1733,7 +1757,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1742,26 +1766,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1770,26 +1794,26 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1805,39 +1829,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>480</v>
+        <v>434</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1856,79 +1880,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>498</v>
+        <v>409</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>499</v>
+        <v>413</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>402</v>
+        <v>505</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -1936,7 +1960,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -1944,7 +1968,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1952,7 +1976,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>503</v>
+        <v>405</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -1960,26 +1984,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>398</v>
+        <v>510</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1998,123 +2022,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3">
-        <v>34.1</v>
+        <v>33.4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.5</v>
+        <v>9.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.0</v>
+        <v>36.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2126,8 +2150,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2139,834 +2163,834 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J3" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J6" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="J7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J8" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="I10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="I12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J12" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J13" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J14" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J15" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="I16" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J16" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>94</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="J17" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J18" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J19" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J20" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J21" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="J22" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="I23" s="3" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="J23" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="J24" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>132</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>133</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="J26" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2974,95 +2998,95 @@
         <v>134</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J27" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J28" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>142</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J29" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
@@ -3073,154 +3097,156 @@
         <v>144</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="I30" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J30" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>144</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J31" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J32" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J33" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>160</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J34" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
@@ -3228,108 +3254,110 @@
         <v>161</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="I35" s="3" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="J35" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>167</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J36" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>169</v>
+        <v>53</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>170</v>
+      </c>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
@@ -3339,1330 +3367,1336 @@
         <v>174</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="J46" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J48" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>99</v>
+        <v>209</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>211</v>
+        <v>125</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>99</v>
+        <v>212</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>122</v>
+        <v>213</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>216</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>218</v>
+        <v>125</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>220</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>104</v>
+        <v>212</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="J54" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>44</v>
+        <v>233</v>
       </c>
       <c r="J57" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="J59" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J60" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>249</v>
+        <v>188</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>95</v>
+        <v>209</v>
       </c>
       <c r="J61" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>251</v>
+        <v>125</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>255</v>
+        <v>125</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>129</v>
+        <v>250</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>104</v>
+        <v>212</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>99</v>
+        <v>209</v>
       </c>
       <c r="J66" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F67" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G67" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J67" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>268</v>
+        <v>125</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="J68" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>271</v>
+        <v>125</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J69" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="J70" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>193</v>
+        <v>270</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J72" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>61</v>
+        <v>275</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>178</v>
+        <v>276</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>104</v>
+        <v>212</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>61</v>
+        <v>281</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J75" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="J77" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>220</v>
+        <v>293</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J79" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>122</v>
+        <v>298</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>302</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="J81" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="D82" s="3" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>306</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="J82" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -4670,56 +4704,56 @@
         <v>307</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>195</v>
+        <v>308</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="J83" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>209</v>
+        <v>311</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="J84" s="3">
         <v>5</v>
@@ -4727,119 +4761,119 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>122</v>
+        <v>313</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>311</v>
+        <v>261</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>226</v>
+        <v>316</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>129</v>
+        <v>317</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>129</v>
+        <v>317</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>316</v>
+        <v>125</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4847,91 +4881,91 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F89" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G89" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="J89" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>323</v>
+        <v>125</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>325</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="J91" s="3">
         <v>5</v>
@@ -4939,29 +4973,29 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>209</v>
+        <v>332</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="J92" s="3">
         <v>5</v>
@@ -4969,423 +5003,423 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>332</v>
+        <v>60</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>295</v>
+        <v>185</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F95" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G95" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>217</v>
+        <v>43</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>332</v>
+        <v>60</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>226</v>
+        <v>346</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>217</v>
+        <v>348</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>332</v>
+        <v>60</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>341</v>
+        <v>290</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>342</v>
+        <v>191</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>303</v>
+        <v>209</v>
       </c>
       <c r="J98" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>203</v>
+        <v>327</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>345</v>
+        <v>185</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>346</v>
+        <v>72</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="J99" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>269</v>
+        <v>353</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>349</v>
+        <v>191</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="J100" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="J101" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>143</v>
+        <v>355</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>325</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="J102" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>357</v>
+        <v>269</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>226</v>
+        <v>362</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="J103" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>220</v>
+        <v>366</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="J104" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>54</v>
+        <v>250</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>364</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J105" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>366</v>
+        <v>150</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>220</v>
+        <v>370</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F106" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G106" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="J106" s="3">
         <v>5</v>
@@ -5393,119 +5427,121 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>295</v>
+        <v>374</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="J107" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>99</v>
+        <v>212</v>
       </c>
       <c r="J108" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>374</v>
+        <v>50</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>178</v>
+        <v>378</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="J109" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>122</v>
+        <v>380</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>377</v>
+        <v>191</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F110" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>382</v>
+      </c>
       <c r="G110" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J110" s="3">
         <v>4</v>
@@ -5513,151 +5549,151 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="J111" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>154</v>
+        <v>387</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>193</v>
+        <v>370</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J112" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>385</v>
+        <v>276</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>325</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="J113" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>220</v>
+        <v>316</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>54</v>
+        <v>317</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="J114" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>92</v>
+        <v>323</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F115" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G115" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J115" s="3">
         <v>1</v>
@@ -5665,36 +5701,66 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>393</v>
+        <v>185</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="J116" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J117" s="3">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J116"/>
+  <autoFilter ref="A1:J117"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5811,6 +5877,7 @@
     <hyperlink ref="H114" r:id="rId113"/>
     <hyperlink ref="H115" r:id="rId114"/>
     <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5818,9 +5885,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5829,36 +5896,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5866,18 +5933,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>174</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5885,334 +5952,201 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>231</v>
+        <v>125</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>252</v>
+        <v>299</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>259</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>178</v>
+        <v>321</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>282</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>193</v>
+        <v>325</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>352</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>314</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>122</v>
+        <v>364</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>232</v>
+        <v>365</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>233</v>
+        <v>366</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>315</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>316</v>
+        <v>399</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6226,13 +6160,6 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6246,103 +6173,103 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>325</v>
+        <v>215</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>163</v>
+        <v>407</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>400</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>364</v>
+        <v>412</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>405</v>
+        <v>382</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -6350,15 +6277,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6366,7 +6293,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6385,23 +6312,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -6409,7 +6336,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6417,15 +6344,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6433,7 +6360,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>127</v>
+        <v>226</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6441,7 +6368,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>290</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6449,7 +6376,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6457,7 +6384,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6465,7 +6392,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6473,7 +6400,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6481,7 +6408,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6489,7 +6416,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6497,7 +6424,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6505,7 +6432,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6526,16 +6453,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
@@ -6543,13 +6470,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -6557,7 +6484,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C3" s="3">
         <v>14.0</v>
@@ -6571,7 +6498,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
         <v>12.5</v>
@@ -6585,7 +6512,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C5" s="3">
         <v>11.3</v>
@@ -6599,7 +6526,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C6" s="3">
         <v>11.2</v>
@@ -6613,7 +6540,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3">
         <v>7.0</v>
@@ -6627,7 +6554,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C8" s="3">
         <v>6.2</v>
@@ -6641,7 +6568,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="3">
         <v>6.0</v>
@@ -6655,7 +6582,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C10" s="3">
         <v>5.8</v>
@@ -6669,13 +6596,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="C11" s="3">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="D11" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6683,7 +6610,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="C12" s="3">
         <v>4.2</v>
@@ -6697,13 +6624,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>290</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -6711,7 +6638,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6725,10 +6652,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6739,10 +6666,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C16" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6762,46 +6689,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>346</v>
+        <v>421</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -6817,55 +6744,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6873,9 +6800,17 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>114</v>
+        <v>250</v>
       </c>
       <c r="B8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6888,7 +6823,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6900,34 +6835,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6935,31 +6870,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -6967,31 +6902,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>425</v>
+        <v>370</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F3" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>429</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4">
@@ -6999,31 +6934,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>280</v>
+        <v>438</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F4" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>429</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5">
@@ -7031,31 +6966,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>193</v>
+        <v>249</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F5" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>44</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6">
@@ -7063,31 +6998,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>295</v>
+        <v>185</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F6" s="3">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
@@ -7095,31 +7030,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>426</v>
-      </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>429</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8">
@@ -7127,31 +7062,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F8" s="3">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>303</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
@@ -7159,31 +7094,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>113</v>
+        <v>459</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="F9" s="3">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>217</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -7191,31 +7126,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>144</v>
+        <v>381</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -7223,31 +7158,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>200</v>
+        <v>305</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>217</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12">
@@ -7255,31 +7190,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>470</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -7287,31 +7222,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>363</v>
+        <v>151</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -7319,31 +7254,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>104</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15">
@@ -7351,31 +7286,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>280</v>
+        <v>478</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F15" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -7383,31 +7318,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>263</v>
+        <v>483</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F16" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>303</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -7415,31 +7350,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>473</v>
+        <v>381</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F17" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>228</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -7447,31 +7382,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>480</v>
+        <v>429</v>
       </c>
       <c r="F18" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>228</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19">
@@ -7479,31 +7414,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>485</v>
+        <v>185</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F19" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20">
@@ -7511,31 +7446,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>489</v>
+        <v>451</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>480</v>
+        <v>429</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
@@ -7543,31 +7478,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>217</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W23.xlsx
+++ b/reports/devops-jobs-israel-2026-W23.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="535">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-02T10:52:13</t>
+    <t xml:space="preserve">2026-06-03T11:20:09</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,12 +57,15 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
+    <t xml:space="preserve">0.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary disclosure rate %</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.0%</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary disclosure rate %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -201,12 +204,27 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
   </si>
   <si>
@@ -237,9 +255,6 @@
     <t xml:space="preserve">Developer Advocate</t>
   </si>
   <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD, Security</t>
   </si>
   <si>
@@ -411,7 +426,7 @@
     <t xml:space="preserve">DevOps Engineer (Remote)</t>
   </si>
   <si>
-    <t xml:space="preserve">Boston, Massachusetts, United States</t>
+    <t xml:space="preserve">Austin, Texas</t>
   </si>
   <si>
     <t xml:space="preserve">Israel (other)</t>
@@ -420,7 +435,7 @@
     <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5710946004</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Data Platform Engineer</t>
@@ -495,15 +510,6 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
   </si>
   <si>
-    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Devops Engineer</t>
   </si>
   <si>
@@ -546,988 +552,1027 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4421628183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Cast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4422419661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autodesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4419692696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4420959611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4419674409</t>
   </si>
   <si>
     <t xml:space="preserve">Medulla</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">eko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4421807840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4418706383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-datateam-4421661564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4419674925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4422661719</t>
   </si>
   <si>
     <t xml:space="preserve">Toluna</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
   </si>
   <si>
-    <t xml:space="preserve">Autodesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloudride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4420959611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4421807840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4418706383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grip Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
+    <t xml:space="preserve">DevOps Specialist - 50400194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Financial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Cloud Architect (25000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25000-at-yael-group-4417626508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4419851508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Rehovot, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-datateam-4421661564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, EWAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-ewaf-at-thales-4345712736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist - 50400194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Financial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloudops-engineer-at-moveo-source-4423883581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4417616930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-rafael-advanced-defense-systems-4421614338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linnovate Technologies</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-mobileye-4409774817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepRec.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramla, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4422328952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-nova-ltd-4422811314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4424019406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Be'er Sheva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberArk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-be-er-sheva-at-cyberark-4378443169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer (Cortex Research)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-cortex-research-at-palo-alto-networks-4361488662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Lead Engineer (DevOps and Process Optimization/Automation) – Bangkok based, relocation provided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-engineer-devops-and-process-optimization-automation-%E2%80%93-bangkok-based-relocation-provided-at-agoda-4411338565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensi.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4419063857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure &amp; AKS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-aks-at-one-digital-4419243639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4409766498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiBob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4418360624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4418395173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roboteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XTEND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4421663350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finubit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-finubit-4420486202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artivion EMEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-apple-4421047611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Interceptor System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skapion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-interceptor-system-engineer-at-skapion-4422362464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4419247188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Systems Infrastructure Engineer (1006270)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-systems-infrastructure-engineer-1006270-at-elad-software-systems-4422877678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377380382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPC Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-cloud-engineer-at-opc-energy-4422582076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4419681559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4419690404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stampli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stampli-4421625305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer - Cloud, XSPM (Hybrid, ISR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-cloud-xspm-hybrid-isr-at-crowdstrike-4418750800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4421620393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4409576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4416809451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4418395173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Be'er Sheva)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-be-er-sheva-at-cyberark-4378443169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer (Cortex Research)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-cortex-research-at-palo-alto-networks-4361488662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Lead Engineer (DevOps and Process Optimization/Automation) – Bangkok based, relocation provided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agoda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-engineer-devops-and-process-optimization-automation-%E2%80%93-bangkok-based-relocation-provided-at-agoda-4411338565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure &amp; AKS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-aks-at-one-digital-4419243639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMware System Administrator (36310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-system-administrator-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4421685538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-engineer-at-gotfriends-4418384231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4Cast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4421628183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramla, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4422328952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4417624412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Cloud Architect (25000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25000-at-yael-group-4417626508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-mobileye-4409774817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-core-team-at-thales-4371458115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4409726747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPC Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-cloud-engineer-at-opc-energy-4422582076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Shemesh, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4418249612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4419247188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377765290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-corsa-4419470455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4418564684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiBob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stampli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stampli-4421625305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer - Cloud, XSPM (Hybrid, ISR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-cloud-xspm-hybrid-isr-at-crowdstrike-4418750800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist - Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orca AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-tier-2-at-orca-ai-4409854863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1536,28 +1581,22 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1709,7 +1748,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -1717,7 +1756,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -1725,7 +1764,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -1733,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>425</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10">
@@ -1741,7 +1780,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1757,7 +1796,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1766,26 +1805,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1794,23 +1833,23 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
         <v>37</v>
@@ -1829,41 +1868,49 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="B5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1880,79 +1927,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="B2" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>409</v>
+        <v>520</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>506</v>
+        <v>424</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>509</v>
+        <v>419</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -1960,31 +2007,31 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>408</v>
+        <v>524</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>405</v>
+        <v>525</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>510</v>
+        <v>415</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -1992,18 +2039,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>511</v>
+        <v>417</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>512</v>
+        <v>423</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2022,54 +2069,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>41</v>
       </c>
       <c r="C2" s="3">
-        <v>15.5</v>
+        <v>13.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -2078,67 +2125,67 @@
         <v>9.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>36.6</v>
+        <v>31.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.7</v>
+        <v>16.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2150,7 +2197,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2163,633 +2210,633 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="J14" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="J18" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J19" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>105</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>106</v>
@@ -2798,7 +2845,7 @@
         <v>107</v>
       </c>
       <c r="J20" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -2812,16 +2859,16 @@
         <v>53</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>111</v>
@@ -2830,7 +2877,7 @@
         <v>112</v>
       </c>
       <c r="J21" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2838,68 +2885,68 @@
         <v>113</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="J22" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="J23" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>121</v>
@@ -2908,25 +2955,25 @@
         <v>122</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>124</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -2937,60 +2984,60 @@
         <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="J25" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>132</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>133</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -2998,191 +3045,191 @@
         <v>134</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>137</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>138</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="J27" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>153</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>154</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -3190,222 +3237,222 @@
         <v>155</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J36" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J37" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>177</v>
+        <v>54</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>180</v>
@@ -3414,88 +3461,88 @@
         <v>181</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>182</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="J40" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="J41" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J42" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>190</v>
@@ -3504,28 +3551,28 @@
         <v>191</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>192</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>193</v>
@@ -3534,58 +3581,58 @@
         <v>194</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>177</v>
+        <v>54</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>195</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>197</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>43</v>
+        <v>189</v>
       </c>
       <c r="J45" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>198</v>
@@ -3594,210 +3641,210 @@
         <v>199</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>200</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="J46" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="J47" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>203</v>
+        <v>67</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>206</v>
+        <v>66</v>
       </c>
       <c r="J48" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>210</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>211</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>212</v>
+        <v>107</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="D51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F51" s="3" t="s">
+      <c r="G51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="I51" s="3" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>125</v>
+        <v>218</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>219</v>
@@ -3806,140 +3853,140 @@
         <v>220</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="C55" s="3" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="J55" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="J57" s="3">
         <v>13</v>
@@ -3947,209 +3994,211 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>236</v>
+        <v>130</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F61" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="G61" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>209</v>
+        <v>86</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>246</v>
+        <v>194</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>212</v>
+        <v>44</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="J64" s="3">
         <v>2</v>
@@ -4157,211 +4206,209 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="J65" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>125</v>
+        <v>251</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>209</v>
+        <v>66</v>
       </c>
       <c r="J66" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>53</v>
+        <v>221</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>125</v>
+        <v>256</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>102</v>
+        <v>224</v>
       </c>
       <c r="J69" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>191</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="J70" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>268</v>
+        <v>67</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>270</v>
+        <v>194</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="J71" s="3">
         <v>6</v>
@@ -4369,301 +4416,303 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>272</v>
+        <v>130</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="J72" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>185</v>
+        <v>272</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>107</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>281</v>
+        <v>61</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="G75" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>43</v>
+        <v>224</v>
       </c>
       <c r="J75" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>191</v>
+        <v>282</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F76" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="G76" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>64</v>
+        <v>284</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="J77" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>291</v>
+        <v>178</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>209</v>
+        <v>112</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="D79" s="3" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>102</v>
+        <v>189</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="I81" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
@@ -4671,89 +4720,89 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>305</v>
+        <v>203</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="J82" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>185</v>
+        <v>238</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>107</v>
       </c>
       <c r="J83" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J84" s="3">
         <v>5</v>
@@ -4761,423 +4810,425 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>313</v>
+        <v>67</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>125</v>
+        <v>310</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>316</v>
+        <v>178</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>317</v>
+        <v>54</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>316</v>
+        <v>178</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>317</v>
+        <v>54</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>125</v>
+        <v>315</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>199</v>
+        <v>317</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F88" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="G88" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>324</v>
+        <v>230</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>325</v>
+        <v>191</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>125</v>
+        <v>322</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>327</v>
+        <v>198</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>209</v>
+        <v>44</v>
       </c>
       <c r="J90" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F91" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="G91" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>102</v>
+        <v>189</v>
       </c>
       <c r="J91" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>102</v>
+        <v>329</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>334</v>
+        <v>67</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>102</v>
+        <v>224</v>
       </c>
       <c r="J93" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="J94" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J95" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>226</v>
+        <v>339</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>227</v>
+        <v>340</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>37</v>
+        <v>341</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="J96" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>60</v>
+        <v>343</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>346</v>
+        <v>276</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>348</v>
+        <v>66</v>
       </c>
       <c r="J97" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>60</v>
+        <v>343</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="J98" s="3">
         <v>2</v>
@@ -5185,59 +5236,59 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="J99" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>353</v>
-      </c>
       <c r="C100" s="3" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -5245,396 +5296,392 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="J101" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>358</v>
+        <v>260</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>359</v>
+        <v>178</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J102" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>362</v>
+        <v>203</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>102</v>
+        <v>224</v>
       </c>
       <c r="J103" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="J104" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J105" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>150</v>
+        <v>366</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>370</v>
+        <v>194</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="J106" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="J107" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>257</v>
+        <v>374</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="J108" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>50</v>
+        <v>343</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>185</v>
+        <v>377</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="J109" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="D110" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="I110" s="3" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="J110" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>191</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="J111" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>370</v>
+        <v>203</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="J112" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B113" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="D113" s="3" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>391</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="J113" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114">
@@ -5645,122 +5692,242 @@
         <v>393</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>316</v>
+        <v>191</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>317</v>
+        <v>54</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>394</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="J114" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>323</v>
+        <v>395</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>212</v>
+        <v>44</v>
       </c>
       <c r="J115" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>161</v>
+        <v>51</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="J116" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F117" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>402</v>
+      </c>
       <c r="G117" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="J117" s="3">
-        <v>0</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J118" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J119" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J120" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J121" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J117"/>
+  <autoFilter ref="A1:J121"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5878,6 +6045,10 @@
     <hyperlink ref="H115" r:id="rId114"/>
     <hyperlink ref="H116" r:id="rId115"/>
     <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5885,9 +6056,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5896,257 +6067,428 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>242</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>262</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>298</v>
+        <v>218</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>299</v>
+        <v>219</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>302</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>313</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>314</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>322</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>325</v>
+        <v>186</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>326</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>352</v>
+        <v>274</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>353</v>
+        <v>275</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>354</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>364</v>
+        <v>284</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>365</v>
+        <v>285</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>366</v>
+        <v>268</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>367</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>399</v>
+        <v>295</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>400</v>
+        <v>296</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>185</v>
+        <v>297</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>401</v>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G22"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6160,6 +6502,15 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6173,15 +6524,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" s="3">
         <v>31</v>
@@ -6189,31 +6540,31 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
@@ -6221,7 +6572,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>170</v>
+        <v>419</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
@@ -6229,23 +6580,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>408</v>
+        <v>172</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -6253,23 +6604,23 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -6277,7 +6628,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6285,7 +6636,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6293,7 +6644,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6306,21 +6657,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -6328,7 +6679,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -6336,7 +6687,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6344,7 +6695,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6352,7 +6703,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6360,7 +6711,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>226</v>
+        <v>140</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6368,7 +6719,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>290</v>
+        <v>156</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6376,7 +6727,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6384,7 +6735,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6392,7 +6743,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6400,7 +6751,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6408,7 +6759,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6416,7 +6767,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6424,7 +6775,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6432,7 +6783,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6446,23 +6797,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2">
@@ -6470,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3">
         <v>22.5</v>
@@ -6484,10 +6835,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
-        <v>14.0</v>
+        <v>12.5</v>
       </c>
       <c r="D3" s="3">
         <v>4</v>
@@ -6498,13 +6849,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="C4" s="3">
-        <v>12.5</v>
+        <v>11.3</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6512,10 +6863,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="C5" s="3">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -6526,10 +6877,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="C6" s="3">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -6540,13 +6891,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="C7" s="3">
-        <v>7.0</v>
+        <v>10.5</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6554,10 +6905,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3">
-        <v>6.2</v>
+        <v>7.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6568,10 +6919,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="C9" s="3">
-        <v>6.0</v>
+        <v>6.2</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6582,7 +6933,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3">
         <v>5.8</v>
@@ -6596,7 +6947,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C11" s="3">
         <v>5.8</v>
@@ -6610,13 +6961,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="C12" s="3">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -6624,13 +6975,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="C13" s="3">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6638,10 +6989,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6652,7 +7003,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6666,7 +7017,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6689,46 +7040,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>421</v>
+        <v>341</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>422</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3">
         <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -6744,31 +7095,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -6776,7 +7127,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6784,7 +7135,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6792,25 +7143,17 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>317</v>
+        <v>221</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6823,7 +7166,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6835,34 +7178,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6870,31 +7213,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -6902,31 +7245,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>433</v>
+        <v>271</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>348</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -6934,31 +7277,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="F4" s="3">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>233</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -6966,31 +7309,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>249</v>
+        <v>186</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F5" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>348</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -6998,31 +7341,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>185</v>
+        <v>456</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="F6" s="3">
         <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>212</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7">
@@ -7030,31 +7373,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>348</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -7062,31 +7405,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="F8" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>233</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -7094,31 +7437,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="F9" s="3">
         <v>57</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -7126,31 +7469,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>381</v>
+        <v>474</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F10" s="3">
         <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -7158,31 +7501,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>305</v>
+        <v>479</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="F11" s="3">
         <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>348</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12">
@@ -7190,31 +7533,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>470</v>
+        <v>156</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F12" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -7222,31 +7565,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>151</v>
+        <v>486</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>152</v>
+        <v>487</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F13" s="3">
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -7254,31 +7597,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>446</v>
+        <v>490</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>212</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15">
@@ -7286,31 +7629,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>191</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -7318,31 +7661,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>483</v>
+        <v>178</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -7350,31 +7693,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>381</v>
+        <v>501</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>43</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18">
@@ -7382,31 +7725,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>107</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19">
@@ -7414,31 +7757,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20">
@@ -7446,31 +7789,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>185</v>
+        <v>297</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>43</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21">
@@ -7478,31 +7821,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>43</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W23.xlsx
+++ b/reports/devops-jobs-israel-2026-W23.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="531">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-03T11:20:09</t>
+    <t xml:space="preserve">2026-06-04T10:09:59</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8%</t>
+    <t xml:space="preserve">1.7%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -426,7 +426,7 @@
     <t xml:space="preserve">DevOps Engineer (Remote)</t>
   </si>
   <si>
-    <t xml:space="preserve">Austin, Texas</t>
+    <t xml:space="preserve">Boston, Massachusetts, United States</t>
   </si>
   <si>
     <t xml:space="preserve">Israel (other)</t>
@@ -435,7 +435,7 @@
     <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5710946004</t>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Data Platform Engineer</t>
@@ -531,6 +531,15 @@
     <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
   </si>
   <si>
@@ -552,286 +561,784 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">eko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autodesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4419674925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4419692696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4422419661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4419674409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4395671057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4418360624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Cast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist - 50400194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Financial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4422931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-datateam-4421661564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepRec.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-nova-ltd-4422811314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-core-team-at-thales-4371458115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-dream-4335498627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4424019406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
     <t xml:space="preserve">Commit</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4421628183</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
+    <t xml:space="preserve">Sensi.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4419063857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finubit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-finubit-4420486202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure &amp; AKS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-aks-at-one-digital-4419243639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4409766498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4421807840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramla, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-at-ngsoft-4419242294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPC Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-cloud-engineer-at-opc-energy-4422582076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiBob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4418395173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roboteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4417616930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XTEND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4421663350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artivion EMEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-apple-4421047611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-system-engineer-at-iai-israel-aerospace-industries-4418729987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4419247188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Systems Infrastructure Engineer (1006270)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-systems-infrastructure-engineer-1006270-at-elad-software-systems-4422877678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTC searching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/frontend-infrastructure-engineer-at-btc-searching-4422498571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377380382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4419681559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4420131505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linnovate Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4421620393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-rafael-advanced-defense-systems-4421614338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4409576965</t>
   </si>
   <si>
     <t xml:space="preserve">CodSec</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
   </si>
   <si>
-    <t xml:space="preserve">4Cast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4422419661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloudride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autodesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4419692696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4420959611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4419674409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4421807840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4418706383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-datateam-4421661564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4419674925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4422661719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist - 50400194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Financial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Cloud Architect (25000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25000-at-yael-group-4417626508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4419851508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
   </si>
   <si>
     <t xml:space="preserve">Mobileye</t>
@@ -840,667 +1347,178 @@
     <t xml:space="preserve">Jerusalem District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-mobileye-4409774817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepRec.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramla, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4422328952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-nova-ltd-4422811314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4424019406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Be'er Sheva)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-be-er-sheva-at-cyberark-4378443169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer (Cortex Research)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-cortex-research-at-palo-alto-networks-4361488662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Lead Engineer (DevOps and Process Optimization/Automation) – Bangkok based, relocation provided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agoda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-engineer-devops-and-process-optimization-automation-%E2%80%93-bangkok-based-relocation-provided-at-agoda-4411338565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensi.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4419063857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure &amp; AKS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-aks-at-one-digital-4419243639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4409766498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiBob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4418360624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4418395173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roboteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XTEND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4421663350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finubit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-finubit-4420486202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artivion EMEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-apple-4421047611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Interceptor System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skapion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-interceptor-system-engineer-at-skapion-4422362464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4419247188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Systems Infrastructure Engineer (1006270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-systems-infrastructure-engineer-1006270-at-elad-software-systems-4422877678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377380382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPC Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-cloud-engineer-at-opc-energy-4422582076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4419681559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4419690404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMware System Administrator (36310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-system-administrator-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4421685538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
     <t xml:space="preserve">Cato Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stampli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stampli-4421625305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer - Cloud, XSPM (Hybrid, ISR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-cloud-xspm-hybrid-isr-at-crowdstrike-4418750800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware System Administrator (36310)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-system-administrator-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4421685538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortinet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
     <t xml:space="preserve">Bria AI</t>
@@ -1512,16 +1530,7 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
+    <t xml:space="preserve">IT Support Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">proteanTecs</t>
@@ -1530,15 +1539,18 @@
     <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
   </si>
   <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -1551,30 +1563,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1584,13 +1572,13 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1748,7 +1736,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
@@ -1756,7 +1744,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1764,7 +1752,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -1772,7 +1760,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10">
@@ -1780,7 +1768,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1844,7 +1832,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -1852,7 +1840,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1871,12 +1859,12 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B2" s="3">
         <v>45</v>
@@ -1884,23 +1872,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1927,31 +1915,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B4" s="3">
         <v>23</v>
@@ -1959,7 +1947,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -1967,7 +1955,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B6" s="3">
         <v>18</v>
@@ -1975,15 +1963,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>424</v>
+        <v>518</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B8" s="3">
         <v>17</v>
@@ -1991,66 +1979,66 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>523</v>
+        <v>422</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>419</v>
+        <v>520</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>524</v>
+        <v>416</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>416</v>
+        <v>521</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>525</v>
+        <v>412</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2075,13 +2063,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2">
@@ -2089,13 +2077,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3">
-        <v>13.4</v>
+        <v>15.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2107,31 +2095,31 @@
         <v>86</v>
       </c>
       <c r="C3" s="3">
-        <v>33.2</v>
+        <v>32.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.2</v>
+        <v>8.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -2140,28 +2128,28 @@
         <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.1</v>
+        <v>34.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
@@ -2170,22 +2158,22 @@
         <v>19.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2269,7 +2257,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -2301,7 +2289,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2333,7 +2321,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -2365,7 +2353,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -2397,7 +2385,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -2429,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2461,7 +2449,7 @@
         <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2493,7 +2481,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -2525,7 +2513,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -2557,7 +2545,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -2589,7 +2577,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -2621,7 +2609,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -2653,7 +2641,7 @@
         <v>86</v>
       </c>
       <c r="J14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2685,7 +2673,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -2717,7 +2705,7 @@
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2749,7 +2737,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2769,7 @@
         <v>44</v>
       </c>
       <c r="J18" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -2813,7 +2801,7 @@
         <v>103</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2845,7 +2833,7 @@
         <v>107</v>
       </c>
       <c r="J20" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2877,7 +2865,7 @@
         <v>112</v>
       </c>
       <c r="J21" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -2909,7 +2897,7 @@
         <v>117</v>
       </c>
       <c r="J22" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -2941,7 +2929,7 @@
         <v>107</v>
       </c>
       <c r="J23" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -2973,7 +2961,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -3005,7 +2993,7 @@
         <v>117</v>
       </c>
       <c r="J25" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -3037,7 +3025,7 @@
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -3066,10 +3054,10 @@
         <v>138</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -3101,7 +3089,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -3133,7 +3121,7 @@
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
@@ -3165,7 +3153,7 @@
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
@@ -3197,7 +3185,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
@@ -3229,7 +3217,7 @@
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
@@ -3261,7 +3249,7 @@
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -3293,7 +3281,7 @@
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
@@ -3325,7 +3313,7 @@
         <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
@@ -3355,7 +3343,7 @@
         <v>44</v>
       </c>
       <c r="J36" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -3363,50 +3351,50 @@
         <v>170</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>24</v>
       </c>
@@ -3414,21 +3402,21 @@
         <v>176</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="J38" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>178</v>
+        <v>54</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>54</v>
@@ -3438,7 +3426,7 @@
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>179</v>
@@ -3447,7 +3435,7 @@
         <v>44</v>
       </c>
       <c r="J39" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -3477,7 +3465,7 @@
         <v>112</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -3488,10 +3476,10 @@
         <v>183</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>63</v>
@@ -3501,10 +3489,10 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>66</v>
+        <v>172</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -3515,13 +3503,13 @@
         <v>130</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>63</v>
@@ -3534,10 +3522,10 @@
         <v>188</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -3545,10 +3533,10 @@
         <v>130</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>54</v>
@@ -3561,13 +3549,13 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3575,10 +3563,10 @@
         <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>54</v>
@@ -3591,13 +3579,13 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -3605,13 +3593,13 @@
         <v>130</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>63</v>
@@ -3621,13 +3609,13 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3635,13 +3623,13 @@
         <v>130</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>63</v>
@@ -3651,27 +3639,27 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>63</v>
@@ -3681,57 +3669,57 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
       <c r="J47" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>130</v>
+        <v>207</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>63</v>
@@ -3744,40 +3732,40 @@
         <v>209</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>107</v>
+        <v>210</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3785,10 +3773,10 @@
         <v>155</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>54</v>
@@ -3797,30 +3785,30 @@
         <v>63</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>107</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>130</v>
+        <v>217</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>54</v>
@@ -3833,27 +3821,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J52" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>218</v>
+        <v>130</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>221</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>63</v>
@@ -3863,32 +3851,34 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
@@ -3896,24 +3886,24 @@
         <v>223</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>224</v>
+        <v>86</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>225</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>54</v>
+        <v>227</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>63</v>
@@ -3923,24 +3913,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>227</v>
+        <v>130</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>54</v>
@@ -3953,43 +3943,43 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>136</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J57" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3997,13 +3987,13 @@
         <v>130</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>191</v>
+        <v>236</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>54</v>
+        <v>237</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>63</v>
@@ -4013,24 +4003,24 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>136</v>
@@ -4043,13 +4033,13 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -4057,13 +4047,13 @@
         <v>130</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>63</v>
@@ -4073,59 +4063,57 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>61</v>
+        <v>247</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>214</v>
-      </c>
+      <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>86</v>
+        <v>239</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>63</v>
@@ -4135,24 +4123,24 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J62" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>54</v>
@@ -4160,29 +4148,31 @@
       <c r="E63" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F63" s="3"/>
+      <c r="F63" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="J63" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>136</v>
@@ -4195,24 +4185,24 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>136</v>
@@ -4225,114 +4215,114 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>221</v>
+        <v>54</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>130</v>
+        <v>272</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>54</v>
@@ -4345,24 +4335,24 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
       <c r="J69" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>54</v>
@@ -4375,40 +4365,40 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>67</v>
+        <v>278</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J71" s="3">
         <v>6</v>
@@ -4416,46 +4406,46 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>267</v>
+        <v>183</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>268</v>
+        <v>184</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>136</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>44</v>
+        <v>239</v>
       </c>
       <c r="J72" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>63</v>
@@ -4465,72 +4455,70 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>136</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>61</v>
+        <v>289</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>214</v>
-      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="J75" s="3">
         <v>3</v>
@@ -4538,48 +4526,46 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>136</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>284</v>
+        <v>130</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>268</v>
+        <v>181</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>63</v>
@@ -4589,24 +4575,24 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>66</v>
+        <v>234</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>287</v>
+        <v>130</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>54</v>
@@ -4619,57 +4605,57 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>67</v>
+        <v>298</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>198</v>
+        <v>299</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>300</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>292</v>
+        <v>130</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>54</v>
+        <v>237</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>63</v>
@@ -4679,27 +4665,27 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>44</v>
+        <v>239</v>
       </c>
       <c r="J80" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>295</v>
+        <v>70</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>297</v>
+        <v>181</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4709,54 +4695,54 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="J82" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>136</v>
@@ -4764,59 +4750,61 @@
       <c r="E83" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>311</v>
+      </c>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="J83" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>306</v>
+        <v>183</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>67</v>
+        <v>315</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>54</v>
@@ -4829,149 +4817,147 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>44</v>
+        <v>239</v>
       </c>
       <c r="J85" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>310</v>
+        <v>130</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>189</v>
+        <v>320</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="J87" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>317</v>
+        <v>181</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>318</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>86</v>
+        <v>239</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>230</v>
+        <v>326</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>191</v>
+        <v>327</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>198</v>
+        <v>330</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>290</v>
+        <v>190</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>63</v>
@@ -4981,102 +4967,102 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="J90" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>324</v>
+        <v>225</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>178</v>
+        <v>333</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>214</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>327</v>
+        <v>255</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="J92" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>67</v>
+        <v>338</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>331</v>
+        <v>181</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="J93" s="3">
         <v>3</v>
@@ -5084,43 +5070,43 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>130</v>
+        <v>341</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>191</v>
+        <v>236</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>54</v>
+        <v>237</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>86</v>
+        <v>337</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>335</v>
+        <v>130</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>54</v>
@@ -5128,61 +5114,61 @@
       <c r="E95" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>214</v>
-      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="J95" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F96" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>136</v>
@@ -5195,114 +5181,114 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>343</v>
+        <v>67</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>178</v>
+        <v>353</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>189</v>
+        <v>355</v>
       </c>
       <c r="J98" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>348</v>
+        <v>130</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="J99" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>213</v>
+        <v>360</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>54</v>
@@ -5315,10 +5301,10 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="J101" s="3">
         <v>3</v>
@@ -5326,13 +5312,13 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>260</v>
+        <v>365</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>54</v>
@@ -5345,27 +5331,27 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="J102" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>63</v>
@@ -5375,24 +5361,24 @@
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="J103" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>361</v>
+        <v>195</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>136</v>
@@ -5405,27 +5391,27 @@
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J104" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>191</v>
+        <v>373</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>63</v>
@@ -5435,24 +5421,24 @@
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="J105" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>54</v>
@@ -5465,24 +5451,24 @@
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J106" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>136</v>
@@ -5495,24 +5481,24 @@
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J107" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>54</v>
@@ -5525,24 +5511,24 @@
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J108" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>136</v>
@@ -5555,24 +5541,24 @@
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J109" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>343</v>
+        <v>387</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>54</v>
@@ -5585,10 +5571,10 @@
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>66</v>
+        <v>172</v>
       </c>
       <c r="J110" s="3">
         <v>0</v>
@@ -5596,13 +5582,13 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>382</v>
+        <v>349</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>383</v>
+        <v>225</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>191</v>
+        <v>390</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>54</v>
@@ -5615,10 +5601,10 @@
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="J111" s="3">
         <v>1</v>
@@ -5626,13 +5612,13 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>136</v>
@@ -5645,70 +5631,70 @@
         <v>23</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J112" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>388</v>
+        <v>130</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>389</v>
+        <v>231</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>390</v>
+        <v>232</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>44</v>
+        <v>172</v>
       </c>
       <c r="J113" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>393</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>66</v>
+        <v>172</v>
       </c>
       <c r="J114" s="3">
         <v>0</v>
@@ -5716,73 +5702,73 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>395</v>
+        <v>130</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>54</v>
+        <v>227</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>44</v>
+        <v>239</v>
       </c>
       <c r="J115" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>178</v>
+        <v>401</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>117</v>
+        <v>239</v>
       </c>
       <c r="J116" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>54</v>
@@ -5790,31 +5776,29 @@
       <c r="E117" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F117" s="3" t="s">
-        <v>402</v>
-      </c>
+      <c r="F117" s="3"/>
       <c r="G117" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="J117" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>54</v>
@@ -5827,107 +5811,47 @@
         <v>23</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="J118" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>406</v>
+        <v>130</v>
       </c>
       <c r="B119" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="D119" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>224</v>
+        <v>86</v>
       </c>
       <c r="J119" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J120" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J121" s="3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J121"/>
+  <autoFilter ref="A1:J119"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6047,8 +5971,6 @@
     <hyperlink ref="H117" r:id="rId116"/>
     <hyperlink ref="H118" r:id="rId117"/>
     <hyperlink ref="H119" r:id="rId118"/>
-    <hyperlink ref="H120" r:id="rId119"/>
-    <hyperlink ref="H121" r:id="rId120"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6056,9 +5978,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -6090,13 +6012,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6104,37 +6026,37 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>65</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6142,7 +6064,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5">
@@ -6150,10 +6072,10 @@
         <v>130</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6161,7 +6083,7 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6">
@@ -6169,10 +6091,10 @@
         <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6180,18 +6102,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>218</v>
+        <v>298</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>219</v>
+        <v>299</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6199,18 +6121,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>222</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>325</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>228</v>
+        <v>326</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>191</v>
+        <v>327</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6218,18 +6140,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>229</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>130</v>
+        <v>332</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>203</v>
+        <v>333</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6237,18 +6159,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>250</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>251</v>
+        <v>371</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>252</v>
+        <v>372</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>186</v>
+        <v>373</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6256,18 +6178,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>253</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>274</v>
+        <v>387</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>275</v>
+        <v>388</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6275,18 +6197,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>277</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>284</v>
+        <v>130</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6294,18 +6216,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>286</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>295</v>
+        <v>396</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>296</v>
+        <v>393</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6313,182 +6235,11 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6502,15 +6253,6 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6524,23 +6266,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6548,7 +6290,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3">
         <v>26</v>
@@ -6556,7 +6298,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B5" s="3">
         <v>24</v>
@@ -6564,7 +6306,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
@@ -6572,7 +6314,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
@@ -6580,7 +6322,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B8" s="3">
         <v>17</v>
@@ -6588,7 +6330,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
@@ -6596,7 +6338,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -6604,7 +6346,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B11" s="3">
         <v>13</v>
@@ -6612,7 +6354,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B12" s="3">
         <v>13</v>
@@ -6620,15 +6362,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6636,7 +6378,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6644,7 +6386,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6657,7 +6399,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6666,7 +6408,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
@@ -6687,15 +6429,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6703,7 +6445,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6711,7 +6453,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6719,7 +6461,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6727,15 +6469,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>225</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6743,7 +6485,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6751,7 +6493,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6759,7 +6501,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6767,7 +6509,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>230</v>
+        <v>167</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6775,7 +6517,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6783,7 +6525,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6797,23 +6539,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
@@ -6961,13 +6703,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C12" s="3">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="D12" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6975,13 +6717,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -6989,10 +6731,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -7003,10 +6745,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -7017,10 +6759,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>260</v>
+        <v>393</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -7043,18 +6785,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -7065,10 +6807,10 @@
         <v>63</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4">
@@ -7076,10 +6818,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -7098,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2">
@@ -7106,7 +6848,7 @@
         <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -7114,7 +6856,7 @@
         <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -7122,20 +6864,20 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -7143,7 +6885,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -7151,9 +6893,17 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -7178,10 +6928,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7193,10 +6943,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -7213,7 +6963,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>73</v>
@@ -7222,19 +6972,19 @@
         <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7245,13 +6995,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>442</v>
@@ -7277,28 +7027,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>449</v>
+        <v>301</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>86</v>
@@ -7309,31 +7059,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="F5" s="3">
-        <v>88</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>112</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6">
@@ -7341,31 +7091,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F6" s="3">
+        <v>88</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="F6" s="3">
-        <v>74</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>459</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>460</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
@@ -7373,31 +7123,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F7" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>460</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8">
@@ -7405,31 +7155,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="F8" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>86</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -7437,31 +7187,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F9" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -7469,31 +7219,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F10" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -7501,31 +7251,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>479</v>
+        <v>214</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="F11" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>460</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
@@ -7533,31 +7283,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>477</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>157</v>
+        <v>333</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>44</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13">
@@ -7565,31 +7315,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>487</v>
+        <v>214</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -7597,31 +7347,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>491</v>
+        <v>156</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F14" s="3">
+        <v>47</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="15">
@@ -7629,31 +7379,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16">
@@ -7661,28 +7411,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>178</v>
+        <v>493</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F16" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7693,31 +7443,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F17" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>232</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -7725,31 +7475,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>504</v>
+        <v>452</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F18" s="3">
+        <v>40</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="F18" s="3">
-        <v>34</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>505</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>205</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19">
@@ -7757,31 +7507,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F19" s="3">
+        <v>34</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="F19" s="3">
-        <v>32</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>509</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
@@ -7789,31 +7539,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>510</v>
+        <v>447</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="F20" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>224</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21">
@@ -7821,31 +7571,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>246</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W23.xlsx
+++ b/reports/devops-jobs-israel-2026-W23.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-04T10:09:59</t>
+    <t xml:space="preserve">2026-06-05T10:08:14</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7%</t>
+    <t xml:space="preserve">0.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -309,21 +309,12 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Architect</t>
+    <t xml:space="preserve">Senior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">Gongio</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
   </si>
   <si>
@@ -561,45 +552,42 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
-    <t xml:space="preserve">eko</t>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autodesk</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autodesk</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
   </si>
   <si>
@@ -615,12 +603,27 @@
     <t xml:space="preserve">Coralogix</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
   </si>
   <si>
+    <t xml:space="preserve">SailPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidome™</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-at-aidome%E2%84%A2-4420742920</t>
+  </si>
+  <si>
     <t xml:space="preserve">Checkmarx</t>
   </si>
   <si>
@@ -642,6 +645,363 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4419692696</t>
   </si>
   <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4421628183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4423379202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest acq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-acq-4423573944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4424126628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist - 50400194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Financial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4423346938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4422931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GK8 by Galaxy (Nasdaq: GLXY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gk8-by-galaxy-nasdaq-glxy-4423387010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-nova-ltd-4422811314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-transmit-security-4338534695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4418360624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-dream-4335498627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepRec.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4424019406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Cast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Compute Runtime)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberArk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-compute-runtime-at-cyberark-4366018220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensi.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4421835860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-engineer-at-gotfriends-4418384231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4419674409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure &amp; AKS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-aks-at-one-digital-4419243639</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Infrastructure Specialist</t>
   </si>
   <si>
@@ -654,49 +1014,202 @@
     <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4422419661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4419247188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Expert -2617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-expert-2617-at-shabak-israeli-security-agency-career-4419681440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roboteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XTEND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4421663350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artivion EMEA</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4419674409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4419694286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Interceptor System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skapion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-interceptor-system-engineer-at-skapion-4422362464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-system-engineer-at-iai-israel-aerospace-industries-4418729987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeker System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/seeker-system-engineer-at-skapion-4422362465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Systems Infrastructure Engineer (1006270)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-systems-infrastructure-engineer-1006270-at-elad-software-systems-4422877678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramla, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-at-ngsoft-4419242294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-applied-materials-israel-4412930033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4419681559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
@@ -705,214 +1218,136 @@
     <t xml:space="preserve">Netanya</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4395671057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4418360624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4Cast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist - 50400194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Financial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4422931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-datateam-4421661564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepRec.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-nova-ltd-4422811314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-core-team-at-thales-4371458115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-dream-4335498627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4424019406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4420191774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiBob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer - Cloud, XSPM (Hybrid, ISR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-cloud-xspm-hybrid-isr-at-crowdstrike-4418750800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
   </si>
   <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
@@ -921,507 +1356,78 @@
     <t xml:space="preserve">Helfy</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior</t>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4421628183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensi.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4419063857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finubit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-finubit-4420486202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure &amp; AKS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-aks-at-one-digital-4419243639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4409766498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4421807840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramla, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-at-ngsoft-4419242294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPC Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-cloud-engineer-at-opc-energy-4422582076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiBob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4418395173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roboteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4398384580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4417616930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XTEND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4421663350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artivion EMEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-apple-4421047611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-system-engineer-at-iai-israel-aerospace-industries-4418729987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4419247188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Systems Infrastructure Engineer (1006270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-systems-infrastructure-engineer-1006270-at-elad-software-systems-4422877678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frontend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BTC searching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/frontend-infrastructure-engineer-at-btc-searching-4422498571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377380382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4419681559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4420131505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linnovate Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4421620393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-rafael-advanced-defense-systems-4421614338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4409576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMware System Administrator (36310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware System Administrator (36310)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
   </si>
   <si>
@@ -1440,21 +1446,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
-    <t xml:space="preserve">Fortinet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
   </si>
   <si>
     <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
   </si>
   <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
   </si>
   <si>
@@ -1473,7 +1479,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4422405627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
@@ -1482,54 +1497,27 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Engineer</t>
   </si>
   <si>
@@ -1542,15 +1530,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
   </si>
   <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -1563,6 +1542,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1572,19 +1560,22 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1736,7 +1727,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7">
@@ -1744,7 +1735,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1752,7 +1743,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -1760,7 +1751,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>458</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10">
@@ -1768,7 +1759,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1840,7 +1831,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1859,31 +1850,31 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1896,9 +1887,17 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1915,55 +1914,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>417</v>
+        <v>513</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
@@ -1971,7 +1970,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>519</v>
+        <v>415</v>
       </c>
       <c r="B8" s="3">
         <v>17</v>
@@ -1979,23 +1978,23 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -2003,42 +2002,42 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>521</v>
+        <v>410</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>412</v>
+        <v>517</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>414</v>
+        <v>518</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2063,13 +2062,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="2">
@@ -2077,13 +2076,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3">
-        <v>15.3</v>
+        <v>14.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2095,85 +2094,85 @@
         <v>86</v>
       </c>
       <c r="C3" s="3">
-        <v>32.3</v>
+        <v>33.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.1</v>
+        <v>9.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.8</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.0</v>
+        <v>30.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.2</v>
+        <v>23.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2185,7 +2184,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2257,7 +2256,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -2289,7 +2288,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2321,7 +2320,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -2353,7 +2352,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -2385,7 +2384,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -2417,7 +2416,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2449,7 +2448,7 @@
         <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2481,7 +2480,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -2513,7 +2512,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -2545,7 +2544,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -2577,7 +2576,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -2609,7 +2608,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -2641,7 +2640,7 @@
         <v>86</v>
       </c>
       <c r="J14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2673,7 +2672,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -2705,7 +2704,7 @@
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2737,7 +2736,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2766,15 +2765,15 @@
         <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>97</v>
@@ -2789,30 +2788,30 @@
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>54</v>
@@ -2821,16 +2820,16 @@
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J20" s="3">
         <v>7</v>
@@ -2838,266 +2837,266 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J21" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="J22" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="J24" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="J26" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>54</v>
@@ -3106,62 +3105,62 @@
         <v>54</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>53</v>
@@ -3185,7 +3184,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -3193,42 +3192,42 @@
         <v>152</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>54</v>
@@ -3249,7 +3248,7 @@
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -3257,16 +3256,16 @@
         <v>160</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>161</v>
@@ -3281,7 +3280,7 @@
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -3289,61 +3288,59 @@
         <v>163</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>164</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J35" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J36" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3351,37 +3348,39 @@
         <v>170</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>54</v>
@@ -3390,11 +3389,9 @@
         <v>54</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>175</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>24</v>
       </c>
@@ -3402,45 +3399,45 @@
         <v>176</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>179</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J39" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>180</v>
@@ -3462,24 +3459,24 @@
         <v>182</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>63</v>
@@ -3489,24 +3486,24 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>54</v>
@@ -3519,27 +3516,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>63</v>
@@ -3549,21 +3546,21 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>181</v>
@@ -3579,27 +3576,27 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J44" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>63</v>
@@ -3612,24 +3609,24 @@
         <v>196</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>63</v>
@@ -3639,24 +3636,24 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>44</v>
+        <v>183</v>
       </c>
       <c r="J46" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>54</v>
@@ -3669,27 +3666,27 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J47" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>63</v>
@@ -3699,27 +3696,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>207</v>
+        <v>127</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>63</v>
@@ -3729,21 +3726,21 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J49" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>181</v>
@@ -3752,31 +3749,31 @@
         <v>54</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>54</v>
@@ -3784,9 +3781,7 @@
       <c r="E51" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>215</v>
-      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
@@ -3794,24 +3789,24 @@
         <v>216</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="J51" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>63</v>
@@ -3824,21 +3819,21 @@
         <v>219</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>54</v>
@@ -3851,24 +3846,24 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>112</v>
+        <v>223</v>
       </c>
       <c r="J53" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>54</v>
@@ -3876,34 +3871,32 @@
       <c r="E54" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>215</v>
-      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>224</v>
+        <v>127</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>63</v>
@@ -3913,10 +3906,10 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J55" s="3">
         <v>0</v>
@@ -3924,13 +3917,13 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>54</v>
@@ -3943,57 +3936,57 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>67</v>
+        <v>232</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>237</v>
+        <v>54</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>63</v>
@@ -4003,27 +3996,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>63</v>
@@ -4033,27 +4026,27 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>63</v>
@@ -4063,57 +4056,57 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>247</v>
+        <v>67</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>249</v>
+        <v>188</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="J61" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>251</v>
+        <v>127</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>63</v>
@@ -4123,10 +4116,10 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
       <c r="J62" s="3">
         <v>1</v>
@@ -4134,10 +4127,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>181</v>
@@ -4146,66 +4139,66 @@
         <v>54</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="J63" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F64" s="3"/>
+      <c r="F64" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="J64" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>63</v>
@@ -4215,57 +4208,59 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>263</v>
+        <v>152</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F66" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="J66" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>67</v>
+        <v>258</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>38</v>
@@ -4275,27 +4270,27 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>172</v>
+        <v>44</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>268</v>
+        <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4305,87 +4300,87 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="J68" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>272</v>
+        <v>67</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J69" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>181</v>
+        <v>269</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J70" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>54</v>
+        <v>210</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>63</v>
@@ -4395,27 +4390,27 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="J71" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>67</v>
+        <v>273</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>184</v>
+        <v>275</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>38</v>
@@ -4425,24 +4420,24 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>239</v>
+        <v>66</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>54</v>
@@ -4455,27 +4450,27 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J73" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>287</v>
+        <v>185</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>38</v>
@@ -4485,27 +4480,27 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>63</v>
@@ -4515,27 +4510,27 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="J75" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>258</v>
+        <v>178</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>38</v>
@@ -4545,117 +4540,117 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="J76" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>130</v>
+        <v>288</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>181</v>
+        <v>269</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>130</v>
+        <v>291</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>181</v>
+        <v>293</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>44</v>
+        <v>183</v>
       </c>
       <c r="J78" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>298</v>
+        <v>127</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>300</v>
+        <v>63</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>172</v>
+        <v>44</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>63</v>
@@ -4665,27 +4660,27 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>70</v>
+        <v>299</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>54</v>
+        <v>210</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4695,24 +4690,24 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="J81" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>275</v>
+        <v>70</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>54</v>
@@ -4725,116 +4720,114 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="J82" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>310</v>
+        <v>188</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>311</v>
-      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="J83" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>183</v>
+        <v>295</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J84" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>54</v>
+        <v>206</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>54</v>
@@ -4842,32 +4835,34 @@
       <c r="E86" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>320</v>
+        <v>86</v>
       </c>
       <c r="J86" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>130</v>
+        <v>313</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>63</v>
@@ -4877,10 +4872,10 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>239</v>
+        <v>86</v>
       </c>
       <c r="J87" s="3">
         <v>3</v>
@@ -4888,16 +4883,16 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>54</v>
+        <v>206</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>63</v>
@@ -4907,27 +4902,27 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="J88" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>327</v>
+        <v>185</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>63</v>
@@ -4937,57 +4932,59 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>190</v>
+        <v>324</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J90" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>225</v>
+        <v>328</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>333</v>
+        <v>191</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>63</v>
@@ -4997,24 +4994,24 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>172</v>
+        <v>330</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>255</v>
+        <v>332</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>54</v>
@@ -5022,47 +5019,47 @@
       <c r="E92" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>337</v>
+        <v>44</v>
       </c>
       <c r="J92" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>181</v>
+        <v>336</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>215</v>
-      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>239</v>
+        <v>86</v>
       </c>
       <c r="J93" s="3">
         <v>3</v>
@@ -5070,16 +5067,16 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>237</v>
+        <v>133</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>38</v>
@@ -5089,27 +5086,27 @@
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>337</v>
+        <v>183</v>
       </c>
       <c r="J94" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>130</v>
+        <v>341</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>63</v>
@@ -5119,10 +5116,10 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="J95" s="3">
         <v>2</v>
@@ -5130,23 +5127,21 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="D96" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>215</v>
-      </c>
+      <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
@@ -5154,24 +5149,24 @@
         <v>348</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J96" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>350</v>
-      </c>
       <c r="C97" s="3" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>63</v>
@@ -5181,18 +5176,18 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>66</v>
+        <v>212</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>67</v>
+        <v>351</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>352</v>
@@ -5204,7 +5199,7 @@
         <v>54</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
@@ -5214,21 +5209,21 @@
         <v>354</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>355</v>
+        <v>66</v>
       </c>
       <c r="J98" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>130</v>
+        <v>355</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>356</v>
+        <v>224</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>54</v>
@@ -5241,10 +5236,10 @@
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="J99" s="3">
         <v>4</v>
@@ -5252,46 +5247,46 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>360</v>
+        <v>191</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>300</v>
+        <v>63</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="J100" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>362</v>
+        <v>190</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>181</v>
+        <v>359</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>63</v>
@@ -5301,27 +5296,27 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="J101" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>214</v>
+        <v>362</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>63</v>
@@ -5331,27 +5326,27 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>66</v>
+        <v>238</v>
       </c>
       <c r="J102" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>214</v>
+        <v>362</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>63</v>
@@ -5361,57 +5356,57 @@
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="J103" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>234</v>
+        <v>66</v>
       </c>
       <c r="J104" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="D105" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>63</v>
@@ -5421,70 +5416,70 @@
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J105" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>44</v>
+        <v>183</v>
       </c>
       <c r="J106" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>380</v>
+        <v>185</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="J107" s="3">
         <v>2</v>
@@ -5492,46 +5487,46 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>382</v>
+        <v>341</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>190</v>
+        <v>378</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J108" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>63</v>
@@ -5541,10 +5536,10 @@
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
       <c r="J109" s="3">
         <v>1</v>
@@ -5552,29 +5547,29 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>387</v>
+        <v>67</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>388</v>
+        <v>217</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J110" s="3">
         <v>0</v>
@@ -5582,16 +5577,16 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>390</v>
+        <v>191</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>63</v>
@@ -5601,70 +5596,70 @@
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J111" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>392</v>
+        <v>51</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="J112" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>130</v>
+        <v>389</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>231</v>
+        <v>390</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J113" s="3">
         <v>0</v>
@@ -5672,16 +5667,16 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>393</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>38</v>
@@ -5691,27 +5686,27 @@
         <v>23</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="J114" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>130</v>
+        <v>395</v>
       </c>
       <c r="B115" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>63</v>
@@ -5724,29 +5719,31 @@
         <v>399</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="J115" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>401</v>
+        <v>188</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F116" s="3"/>
+      <c r="F116" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="G116" s="3" t="s">
         <v>23</v>
       </c>
@@ -5754,21 +5751,21 @@
         <v>402</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="J116" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>403</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>54</v>
@@ -5787,7 +5784,7 @@
         <v>44</v>
       </c>
       <c r="J117" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118">
@@ -5798,7 +5795,7 @@
         <v>406</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>54</v>
@@ -5814,44 +5811,14 @@
         <v>407</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>234</v>
+        <v>86</v>
       </c>
       <c r="J118" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J119" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J119"/>
+  <autoFilter ref="A1:J118"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5970,7 +5937,6 @@
     <hyperlink ref="H116" r:id="rId115"/>
     <hyperlink ref="H117" r:id="rId116"/>
     <hyperlink ref="H118" r:id="rId117"/>
-    <hyperlink ref="H119" r:id="rId118"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5978,9 +5944,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -6012,32 +5978,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -6045,18 +6011,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>224</v>
+        <v>127</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6064,18 +6030,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6083,18 +6049,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>232</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6102,18 +6068,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>298</v>
+        <v>239</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6121,18 +6087,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>325</v>
+        <v>67</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>326</v>
+        <v>245</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>327</v>
+        <v>188</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6140,18 +6106,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>328</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>332</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>333</v>
+        <v>181</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6159,18 +6125,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>334</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>371</v>
+        <v>152</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>372</v>
+        <v>256</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>373</v>
+        <v>188</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6178,18 +6144,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>374</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>387</v>
+        <v>232</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>388</v>
+        <v>271</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6197,18 +6163,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>389</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>130</v>
+        <v>291</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6216,18 +6182,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>396</v>
+        <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>393</v>
+        <v>302</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>253</v>
+        <v>185</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6235,11 +6201,163 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>397</v>
       </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>399</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G21"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6253,6 +6371,14 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6266,23 +6392,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6290,7 +6416,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B4" s="3">
         <v>26</v>
@@ -6298,15 +6424,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
@@ -6314,7 +6440,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
@@ -6322,15 +6448,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
@@ -6338,7 +6464,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -6346,7 +6472,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B11" s="3">
         <v>13</v>
@@ -6354,7 +6480,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B12" s="3">
         <v>13</v>
@@ -6362,15 +6488,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6378,7 +6504,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6386,7 +6512,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6399,7 +6525,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6408,7 +6534,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2">
@@ -6437,7 +6563,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6445,7 +6571,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6453,31 +6579,31 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>97</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>225</v>
+        <v>111</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6485,7 +6611,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6493,7 +6619,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6501,7 +6627,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6509,7 +6635,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6517,7 +6643,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6525,7 +6651,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6539,23 +6665,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2">
@@ -6591,7 +6717,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3">
         <v>11.3</v>
@@ -6605,10 +6731,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -6619,10 +6745,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -6633,13 +6759,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="C7" s="3">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6661,7 +6787,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C9" s="3">
         <v>6.2</v>
@@ -6675,7 +6801,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C10" s="3">
         <v>5.8</v>
@@ -6689,7 +6815,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C11" s="3">
         <v>5.8</v>
@@ -6703,13 +6829,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C12" s="3">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6717,13 +6843,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="C13" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6731,7 +6857,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6745,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>231</v>
+        <v>289</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -6759,7 +6885,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>393</v>
+        <v>295</v>
       </c>
       <c r="C16" s="3">
         <v>2.8</v>
@@ -6785,18 +6911,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6807,10 +6933,10 @@
         <v>63</v>
       </c>
       <c r="B3" s="3">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4">
@@ -6818,10 +6944,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -6840,7 +6966,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2">
@@ -6848,60 +6974,60 @@
         <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>210</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>122</v>
+        <v>398</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6928,10 +7054,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6943,10 +7069,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6963,7 +7089,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>73</v>
@@ -6972,19 +7098,19 @@
         <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6995,28 +7121,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>60</v>
@@ -7027,13 +7153,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>298</v>
+        <v>443</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>299</v>
+        <v>444</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>214</v>
+        <v>353</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>445</v>
@@ -7048,7 +7174,7 @@
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>301</v>
+        <v>447</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>86</v>
@@ -7059,31 +7185,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>355</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
@@ -7091,31 +7217,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>236</v>
+        <v>397</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="F6" s="3">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>112</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7">
@@ -7123,31 +7249,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="F7" s="3">
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>355</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
@@ -7155,31 +7281,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="F8" s="3">
         <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>355</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -7187,28 +7313,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="F9" s="3">
         <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>86</v>
@@ -7219,13 +7345,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>445</v>
@@ -7234,13 +7360,13 @@
         <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7251,31 +7377,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F11" s="3">
         <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -7283,31 +7409,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>477</v>
+        <v>317</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>333</v>
+        <v>228</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="F12" s="3">
         <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>355</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13">
@@ -7315,28 +7441,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>214</v>
+        <v>353</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="F13" s="3">
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>66</v>
@@ -7347,31 +7473,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>156</v>
+        <v>245</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15">
@@ -7379,19 +7505,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>487</v>
+        <v>344</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>436</v>
-      </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>489</v>
@@ -7400,10 +7526,10 @@
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>490</v>
+        <v>348</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
@@ -7411,28 +7537,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>492</v>
+        <v>153</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>493</v>
+        <v>154</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F16" s="3">
         <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7443,31 +7569,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F17" s="3">
         <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
@@ -7475,31 +7601,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>452</v>
+        <v>496</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>500</v>
+        <v>476</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -7507,31 +7633,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F19" s="3">
         <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20">
@@ -7539,31 +7665,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>447</v>
+        <v>503</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="F20" s="3">
         <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21">
@@ -7571,31 +7697,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>510</v>
+        <v>475</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>190</v>
+        <v>275</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W23.xlsx
+++ b/reports/devops-jobs-israel-2026-W23.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="517">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-05T10:08:14</t>
+    <t xml:space="preserve">2026-06-07T09:29:51</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -417,7 +417,7 @@
     <t xml:space="preserve">DevOps Engineer (Remote)</t>
   </si>
   <si>
-    <t xml:space="preserve">Boston, Massachusetts, United States</t>
+    <t xml:space="preserve">Washington, United States</t>
   </si>
   <si>
     <t xml:space="preserve">Israel (other)</t>
@@ -426,7 +426,10 @@
     <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010969004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Data Platform Engineer</t>
@@ -444,18 +447,6 @@
     <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Helm, Istio, Service Mesh, Security, Argo CD, Observability, Karpenter, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8323401002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8432893002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Data Infra Engineer</t>
   </si>
   <si>
@@ -477,15 +468,24 @@
     <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevSecOps</t>
   </si>
   <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
   </si>
   <si>
@@ -552,6 +552,93 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4421628183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4423379202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-devops-engineer-at-abra-4425003795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Cast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
@@ -561,49 +648,307 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer-2617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2617-at-shabak-israeli-security-agency-career-4419681440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist - 50400194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Financial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4422931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4424698066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4419674925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-nova-ltd-4422811314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GK8 by Galaxy (Nasdaq: GLXY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gk8-by-galaxy-nasdaq-glxy-4423387010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-transmit-security-4338534695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-dream-4335498627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepRec.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4424019406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensi.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4421835860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer &amp; Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-tech-lead-at-mobileye-4366001366</t>
   </si>
   <si>
     <t xml:space="preserve">Autodesk</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
   </si>
   <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4419674925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-workday-4420737999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
   </si>
   <si>
     <t xml:space="preserve">SailPoint</t>
@@ -612,16 +957,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidome™</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-at-aidome%E2%84%A2-4420742920</t>
+    <t xml:space="preserve">Staff Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4409766498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
   </si>
   <si>
     <t xml:space="preserve">Checkmarx</t>
@@ -630,925 +996,523 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4419692696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4421628183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4423379202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4420131505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roboteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XTEND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4421663350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artivion EMEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Moon Active</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-system-engineer-at-iai-israel-aerospace-industries-4418729987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeker System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skapion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/seeker-system-engineer-at-skapion-4422362465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Systems Infrastructure Engineer (1006270)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-systems-infrastructure-engineer-1006270-at-elad-software-systems-4422877678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTC searching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/frontend-infrastructure-engineer-at-btc-searching-4422498571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-commit-4425110784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4419681559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4420191774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer - Cloud, XSPM (Hybrid, ISR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-cloud-xspm-hybrid-isr-at-crowdstrike-4418750800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Git, Terraform/IaC, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/production-support-engineer-at-extreme-4418657999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristocrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest acq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-acq-4423573944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4424126628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist - 50400194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Financial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-50400194-at-phoenix-financial-4408375556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4423346938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4422931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GK8 by Galaxy (Nasdaq: GLXY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gk8-by-galaxy-nasdaq-glxy-4423387010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-nova-ltd-4422811314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-transmit-security-4338534695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4418360624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-dream-4335498627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepRec.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4424019406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-check-point-software-4418736258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4Cast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4cast-4415288257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Compute Runtime)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-compute-runtime-at-cyberark-4366018220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensi.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4421835860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-engineer-at-gotfriends-4418384231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4419674409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure &amp; AKS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-aks-at-one-digital-4419243639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4419247188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Expert -2617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-expert-2617-at-shabak-israeli-security-agency-career-4419681440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roboteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XTEND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4421663350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artivion EMEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4419694286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Interceptor System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skapion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-interceptor-system-engineer-at-skapion-4422362464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-system-engineer-at-iai-israel-aerospace-industries-4418729987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seeker System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/seeker-system-engineer-at-skapion-4422362465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Systems Infrastructure Engineer (1006270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-systems-infrastructure-engineer-1006270-at-elad-software-systems-4422877678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramla, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-at-ngsoft-4419242294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-applied-materials-israel-4412930033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4419681559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4420191774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiBob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-hibob-4409901532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer - Cloud, XSPM (Hybrid, ISR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-cloud-xspm-hybrid-isr-at-crowdstrike-4418750800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4398384580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware System Administrator (36310)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-system-administrator-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4421685538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4422405627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+    <t xml:space="preserve">Modellama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-modellama-4361100331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1560,12 +1524,12 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
@@ -1576,6 +1540,9 @@
   </si>
   <si>
     <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1727,7 +1694,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -1735,7 +1702,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1743,7 +1710,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -1751,7 +1718,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>478</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10">
@@ -1823,7 +1790,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -1831,7 +1798,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1850,44 +1817,44 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="B4" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1895,7 +1862,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1914,71 +1881,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="B2" s="3">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>512</v>
+        <v>404</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>414</v>
+        <v>503</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -1986,47 +1953,47 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>420</v>
+        <v>505</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -2034,7 +2001,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -2062,13 +2029,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2">
@@ -2076,13 +2043,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2091,88 +2058,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.8</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>1.9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.6</v>
+        <v>33.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2185,7 +2152,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2256,7 +2223,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2255,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -2320,7 +2287,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -2352,7 +2319,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -2384,7 +2351,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -2416,7 +2383,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2448,7 +2415,7 @@
         <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2480,7 +2447,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -2512,7 +2479,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -2544,7 +2511,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -2576,7 +2543,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -2608,7 +2575,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -2640,7 +2607,7 @@
         <v>86</v>
       </c>
       <c r="J14" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -2672,7 +2639,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -2704,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -2736,7 +2703,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2768,7 +2735,7 @@
         <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -2800,7 +2767,7 @@
         <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2832,7 +2799,7 @@
         <v>109</v>
       </c>
       <c r="J20" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -2864,7 +2831,7 @@
         <v>114</v>
       </c>
       <c r="J21" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -2896,7 +2863,7 @@
         <v>104</v>
       </c>
       <c r="J22" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -2928,7 +2895,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -2960,7 +2927,7 @@
         <v>114</v>
       </c>
       <c r="J24" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -2992,7 +2959,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -3021,21 +2988,21 @@
         <v>135</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="J26" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>133</v>
@@ -3044,30 +3011,30 @@
         <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>54</v>
@@ -3076,62 +3043,62 @@
         <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>54</v>
@@ -3140,62 +3107,62 @@
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="J30" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>54</v>
@@ -3204,88 +3171,86 @@
         <v>63</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>161</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J34" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>164</v>
@@ -3297,58 +3262,60 @@
         <v>165</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J35" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F36" s="3"/>
+      <c r="F36" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>54</v>
@@ -3357,33 +3324,31 @@
         <v>54</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>172</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="J37" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>54</v>
@@ -3393,16 +3358,16 @@
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
@@ -3410,13 +3375,13 @@
         <v>127</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>63</v>
@@ -3426,13 +3391,13 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -3440,10 +3405,10 @@
         <v>127</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>54</v>
@@ -3456,13 +3421,13 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -3470,10 +3435,10 @@
         <v>127</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>54</v>
@@ -3486,10 +3451,10 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="J41" s="3">
         <v>2</v>
@@ -3497,16 +3462,16 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>63</v>
@@ -3516,13 +3481,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="J42" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3530,13 +3495,13 @@
         <v>127</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>63</v>
@@ -3546,13 +3511,13 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -3560,10 +3525,10 @@
         <v>127</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>54</v>
@@ -3576,13 +3541,13 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="J44" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -3590,10 +3555,10 @@
         <v>127</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>54</v>
@@ -3606,24 +3571,24 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J45" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>133</v>
@@ -3636,13 +3601,13 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
@@ -3650,13 +3615,13 @@
         <v>127</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>63</v>
@@ -3666,27 +3631,27 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J47" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>63</v>
@@ -3696,27 +3661,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>127</v>
+        <v>212</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>210</v>
+        <v>54</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>63</v>
@@ -3726,27 +3691,27 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>63</v>
@@ -3756,13 +3721,13 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3770,13 +3735,13 @@
         <v>127</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>63</v>
@@ -3786,24 +3751,24 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>127</v>
+        <v>223</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>133</v>
@@ -3816,24 +3781,24 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="J52" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>54</v>
@@ -3846,24 +3811,24 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="J53" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>54</v>
@@ -3871,15 +3836,17 @@
       <c r="E54" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="J54" s="3">
         <v>5</v>
@@ -3887,16 +3854,16 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>63</v>
@@ -3906,57 +3873,57 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>232</v>
+        <v>127</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>210</v>
+        <v>54</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>63</v>
@@ -3966,27 +3933,27 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>235</v>
+        <v>127</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>63</v>
@@ -3996,27 +3963,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>238</v>
+        <v>66</v>
       </c>
       <c r="J58" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>239</v>
+        <v>127</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>210</v>
+        <v>54</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>63</v>
@@ -4026,10 +3993,10 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
@@ -4037,13 +4004,13 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>133</v>
@@ -4056,10 +4023,10 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="J60" s="3">
         <v>4</v>
@@ -4070,10 +4037,10 @@
         <v>67</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>54</v>
@@ -4086,132 +4053,132 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>67</v>
+        <v>253</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>181</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>54</v>
+        <v>258</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>252</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>226</v>
+        <v>44</v>
       </c>
       <c r="J64" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>235</v>
+        <v>154</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="J65" s="3">
         <v>2</v>
@@ -4219,75 +4186,73 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>252</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J67" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>67</v>
+        <v>268</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>133</v>
@@ -4300,87 +4265,87 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>226</v>
+        <v>66</v>
       </c>
       <c r="J68" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>67</v>
+        <v>272</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>210</v>
+        <v>54</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>63</v>
@@ -4390,27 +4355,27 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>273</v>
+        <v>67</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>275</v>
+        <v>178</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>38</v>
@@ -4420,54 +4385,54 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>188</v>
+        <v>286</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="J73" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>54</v>
@@ -4480,57 +4445,57 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="J74" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>212</v>
+        <v>44</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>178</v>
+        <v>295</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>38</v>
@@ -4540,117 +4505,117 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="J76" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>288</v>
+        <v>127</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>269</v>
+        <v>178</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>293</v>
+        <v>220</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>127</v>
+        <v>302</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="J79" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>127</v>
+        <v>305</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>210</v>
+        <v>54</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>63</v>
@@ -4660,84 +4625,84 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>212</v>
+        <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>300</v>
+        <v>206</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>210</v>
+        <v>133</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J81" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>54</v>
@@ -4750,24 +4715,24 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="J83" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>295</v>
+        <v>177</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>54</v>
@@ -4780,54 +4745,54 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J84" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>227</v>
+        <v>318</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>61</v>
+        <v>320</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>54</v>
@@ -4836,33 +4801,33 @@
         <v>63</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="J86" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>313</v>
+        <v>127</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>63</v>
@@ -4872,27 +4837,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>316</v>
+        <v>127</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>228</v>
+        <v>326</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>63</v>
@@ -4902,211 +4867,207 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>319</v>
+        <v>67</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>320</v>
+        <v>206</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>325</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>327</v>
+        <v>67</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>191</v>
+        <v>333</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="J91" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>188</v>
+        <v>266</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>252</v>
-      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J92" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>133</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>63</v>
+        <v>342</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>63</v>
@@ -5116,57 +5077,57 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>346</v>
+        <v>178</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>347</v>
+        <v>63</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="J96" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>188</v>
+        <v>355</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>63</v>
@@ -5176,24 +5137,24 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="J97" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>353</v>
+        <v>197</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>54</v>
@@ -5206,10 +5167,10 @@
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="J98" s="3">
         <v>2</v>
@@ -5217,16 +5178,16 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>224</v>
+        <v>354</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>188</v>
+        <v>360</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>63</v>
@@ -5236,10 +5197,10 @@
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="J99" s="3">
         <v>4</v>
@@ -5247,46 +5208,46 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>226</v>
+        <v>66</v>
       </c>
       <c r="J100" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>190</v>
+        <v>366</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>359</v>
+        <v>200</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>63</v>
@@ -5296,27 +5257,27 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>361</v>
+        <v>180</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>362</v>
+        <v>181</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>63</v>
@@ -5326,84 +5287,84 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>238</v>
+        <v>136</v>
       </c>
       <c r="J102" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>362</v>
+        <v>178</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="J103" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>66</v>
       </c>
       <c r="J104" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>371</v>
+        <v>192</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>133</v>
@@ -5416,144 +5377,144 @@
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="J105" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>181</v>
+        <v>266</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="J106" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>376</v>
+        <v>243</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="J107" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>341</v>
+        <v>51</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>378</v>
+        <v>178</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="J108" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>382</v>
+        <v>178</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="J109" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>67</v>
+        <v>388</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>217</v>
+        <v>389</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>133</v>
@@ -5566,27 +5527,27 @@
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="J110" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>289</v>
+        <v>392</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>133</v>
+        <v>258</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>63</v>
@@ -5596,10 +5557,10 @@
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="J111" s="3">
         <v>2</v>
@@ -5607,13 +5568,13 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>51</v>
+        <v>394</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>54</v>
@@ -5626,199 +5587,17 @@
         <v>23</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="J112" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J113" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J114" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J115" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J116" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J117" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J118" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J118"/>
+  <autoFilter ref="A1:J112"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5931,12 +5710,6 @@
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
     <hyperlink ref="H112" r:id="rId111"/>
-    <hyperlink ref="H113" r:id="rId112"/>
-    <hyperlink ref="H114" r:id="rId113"/>
-    <hyperlink ref="H115" r:id="rId114"/>
-    <hyperlink ref="H116" r:id="rId115"/>
-    <hyperlink ref="H117" r:id="rId116"/>
-    <hyperlink ref="H118" r:id="rId117"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5944,8 +5717,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5978,51 +5751,51 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6030,18 +5803,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6049,18 +5822,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>232</v>
+        <v>127</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6068,18 +5841,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>209</v>
+        <v>295</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6087,18 +5860,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>241</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>67</v>
+        <v>302</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>245</v>
+        <v>303</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6106,18 +5879,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>246</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>67</v>
+        <v>317</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6125,18 +5898,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>251</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>152</v>
+        <v>368</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6144,18 +5917,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>257</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>232</v>
+        <v>381</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6163,201 +5936,11 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6369,16 +5952,6 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6392,47 +5965,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
@@ -6440,15 +6013,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>404</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
@@ -6456,7 +6029,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>415</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
@@ -6464,7 +6037,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -6472,7 +6045,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B11" s="3">
         <v>13</v>
@@ -6480,15 +6053,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -6496,7 +6069,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6504,15 +6077,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6525,7 +6098,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6534,7 +6107,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
@@ -6555,15 +6128,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6571,7 +6144,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6611,7 +6184,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6635,7 +6208,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6643,7 +6216,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6651,7 +6224,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>221</v>
+        <v>354</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6665,23 +6238,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
@@ -6703,10 +6276,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="C3" s="3">
-        <v>12.5</v>
+        <v>14.0</v>
       </c>
       <c r="D3" s="3">
         <v>4</v>
@@ -6717,13 +6290,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -6745,13 +6318,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="C6" s="3">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6759,10 +6332,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3">
-        <v>7.2</v>
+        <v>7.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -6773,10 +6346,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="C8" s="3">
-        <v>7.0</v>
+        <v>6.2</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6787,10 +6360,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C9" s="3">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6801,7 +6374,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C10" s="3">
         <v>5.8</v>
@@ -6815,13 +6388,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="C11" s="3">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6857,7 +6430,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>217</v>
+        <v>374</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6871,13 +6444,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>289</v>
+        <v>138</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6885,10 +6458,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>295</v>
+        <v>180</v>
       </c>
       <c r="C16" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6911,15 +6484,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6933,10 +6506,10 @@
         <v>63</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4">
@@ -6944,10 +6517,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -6966,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
@@ -6974,7 +6547,7 @@
         <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -6982,15 +6555,15 @@
         <v>133</v>
       </c>
       <c r="B3" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -7003,7 +6576,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>206</v>
+        <v>165</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -7011,23 +6584,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>398</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -7042,7 +6615,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -7054,10 +6627,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7069,10 +6642,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -7089,7 +6662,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>73</v>
@@ -7098,19 +6671,19 @@
         <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7121,28 +6694,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>438</v>
+        <v>294</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>439</v>
+        <v>295</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>60</v>
@@ -7153,31 +6726,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>86</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5">
@@ -7185,31 +6758,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>448</v>
+        <v>329</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>449</v>
+        <v>330</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>181</v>
+        <v>435</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="F5" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>452</v>
+        <v>331</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6">
@@ -7217,31 +6790,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>397</v>
+        <v>257</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="F6" s="3">
         <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>457</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7">
@@ -7249,31 +6822,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F7" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>212</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8">
@@ -7281,31 +6854,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>457</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9">
@@ -7313,31 +6886,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>191</v>
+        <v>286</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="F9" s="3">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10">
@@ -7345,28 +6918,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F10" s="3">
         <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7377,31 +6950,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>476</v>
+        <v>300</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F11" s="3">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>212</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12">
@@ -7409,31 +6982,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>317</v>
+        <v>464</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>457</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13">
@@ -7441,31 +7014,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>482</v>
+        <v>339</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>483</v>
+        <v>340</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="F13" s="3">
+        <v>50</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="F13" s="3">
-        <v>52</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>485</v>
+        <v>343</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14">
@@ -7473,31 +7046,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>245</v>
+        <v>150</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="F14" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -7505,31 +7078,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>344</v>
+        <v>472</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>345</v>
+        <v>473</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>346</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>488</v>
+        <v>423</v>
       </c>
       <c r="F15" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>348</v>
+        <v>475</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -7537,31 +7110,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>153</v>
+        <v>477</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17">
@@ -7569,31 +7142,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18">
@@ -7601,31 +7174,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>185</v>
+        <v>270</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>44</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19">
@@ -7633,31 +7206,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>330</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20">
@@ -7665,31 +7238,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>468</v>
+        <v>423</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>330</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
@@ -7697,31 +7270,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>507</v>
+        <v>191</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>226</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
